--- a/business_forms/034_financial_statement_access_form--business_forms.xlsx
+++ b/business_forms/034_financial_statement_access_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,11 +437,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
     <col width="29" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -520,7 +520,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>financial_statement_access_form_1</t>
+          <t>request_access</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -543,7 +543,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>financial_statement_access_form_2</t>
+          <t>financial_documents</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>financial_statement_access_form_3</t>
+          <t>access_level</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>financial_statement_access_form_4</t>
+          <t>request_reason</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -612,7 +612,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>financial_statement_access_form_5</t>
+          <t>contact_info</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>financial_statement_access_form_6</t>
+          <t>phone_number</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -658,7 +658,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>financial_statement_access_form_7</t>
+          <t>additional_info</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>financial_statement_access_form_8</t>
+          <t>acceptance</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>financial_statement_access_form_9</t>
+          <t>request_date</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>financial_statement_access_form_10</t>
+          <t>access_granted_date</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>financial_statement_access_form_11</t>
+          <t>access_level_hint</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>financial_statement_access_form_12</t>
+          <t>request_reason_hint</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>financial_statement_access_form_13</t>
+          <t>contact_info_hint</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>financial_statement_access_form_14</t>
+          <t>phone_number_hint</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>financial_statement_access_form_15</t>
+          <t>additional_info_hint</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>financial_statement_access_form_16</t>
+          <t>acceptance_hint</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>financial_statement_access_form_17</t>
+          <t>request_date_hint</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>financial_statement_access_form_18</t>
+          <t>access_granted_date_hint</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -921,167 +921,6 @@
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>financial_statement_access_form_19</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Access Level Hint</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>financial_statement_access_form_20</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Financial Documents Hint</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>financial_statement_access_form_21</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Acceptance Hint</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>financial_statement_access_form_22</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Access Level</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>financial_statement_access_form_23</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Request Reason Hint</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>financial_statement_access_form_24</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Contact Information Hint</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>financial_statement_access_form_25</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Phone Number Hint</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1101,7 +940,7 @@
   <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="43" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1126,7 +965,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>financial_statement_access_form_2_choices</t>
+          <t>financial_documents_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1143,7 +982,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>financial_statement_access_form_2_choices</t>
+          <t>financial_documents_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1160,7 +999,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>financial_statement_access_form_2_choices</t>
+          <t>financial_documents_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1177,7 +1016,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>financial_statement_access_form_3_choices</t>
+          <t>access_level_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1194,7 +1033,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>financial_statement_access_form_3_choices</t>
+          <t>access_level_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1211,7 +1050,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>financial_statement_access_form_3_choices</t>
+          <t>access_level_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1228,7 +1067,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>financial_statement_access_form_8_choices</t>
+          <t>acceptance_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1245,7 +1084,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>financial_statement_access_form_8_choices</t>
+          <t>acceptance_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1262,7 +1101,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>financial_statement_access_form_8_choices</t>
+          <t>acceptance_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
